--- a/PPREstimation/output/top10/13_1_Chilean_Patagonia_(1980).xlsx
+++ b/PPREstimation/output/top10/13_1_Chilean_Patagonia_(1980).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -701,7 +700,6 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>3.05301375825107</v>
       </c>
@@ -869,7 +866,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>5.0709234754017</v>
       </c>
@@ -953,7 +949,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>2.37654915350518</v>
       </c>
@@ -1037,7 +1032,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>3.211073402506359</v>
       </c>
@@ -1121,7 +1115,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>4.392729061976549</v>
       </c>
@@ -1205,7 +1198,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>3.669366598269124</v>
       </c>
@@ -1289,7 +1281,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>3.901589893914014</v>
       </c>
@@ -1373,7 +1364,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>3</v>
       </c>
@@ -1457,7 +1447,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
         <v>3.443313791178113</v>
       </c>
@@ -1541,7 +1530,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
         <v>2</v>
       </c>
@@ -1625,7 +1613,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
         <v>3.08179787828029</v>
       </c>
@@ -1709,7 +1696,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
         <v>2.786711334450028</v>
       </c>
@@ -1793,7 +1779,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
         <v>2.111111111111111</v>
       </c>
@@ -1877,7 +1862,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
@@ -1953,7 +1937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2091,6 +2075,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2101,9 +2095,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -2134,19 +2125,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2159,9 +2150,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -2211,6 +2199,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2223,11 +2214,8 @@
           <t>Sea lions</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>13241.91133940488</v>
+        <v>178.0978511623711</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -2235,7 +2223,6 @@
       <c r="H4" s="2" t="n">
         <v>228.8693060905799</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -2274,6 +2261,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13241.91133940486</v>
       </c>
     </row>
     <row r="5">
@@ -2285,11 +2275,8 @@
           <t>Southern hake</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>14544.03408340348</v>
+        <v>353.670638074427</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>958.3944522095351</v>
@@ -2338,6 +2325,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>3033.820665760475</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14544.03408340346</v>
       </c>
     </row>
     <row r="6">
@@ -2349,11 +2339,8 @@
           <t>Skates</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>2885.553430351608</v>
+        <v>46.19996486113047</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>28888.39890319232</v>
@@ -2402,6 +2389,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>40467.41922212073</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2885.553430351604</v>
       </c>
     </row>
     <row r="7">
@@ -2413,11 +2403,8 @@
           <t>Kingklip</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>4428.40234873583</v>
+        <v>75.67944615516947</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>814.5074110174779</v>
@@ -2466,6 +2453,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>1732.910230996607</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4428.402348735824</v>
       </c>
     </row>
     <row r="8">
@@ -2477,11 +2467,8 @@
           <t>Southern blue whiting</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>4486.805516272962</v>
+        <v>180.5758187882512</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>556.8837016496033</v>
@@ -2530,6 +2517,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>783.28056812431</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4486.805516272958</v>
       </c>
     </row>
     <row r="9">
@@ -2541,11 +2531,8 @@
           <t>Hoki (a)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>4035.248744341655</v>
+        <v>131.2509216816987</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>4916.160263611845</v>
@@ -2594,6 +2581,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>6715.336735085121</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4035.248744341651</v>
       </c>
     </row>
     <row r="10">
@@ -2605,11 +2595,8 @@
           <t>Hoki (j)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>1437.389185200233</v>
+        <v>82.9094175930081</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>98.10068489894016</v>
@@ -2658,6 +2645,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>133.1870076345493</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1437.389185200231</v>
       </c>
     </row>
     <row r="11">
@@ -2669,9 +2659,6 @@
           <t>Other demersal fish</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
@@ -2721,6 +2708,9 @@
         <v>0</v>
       </c>
       <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2733,11 +2723,8 @@
           <t>Small pelagic fish</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>612.149101761085</v>
+        <v>49.47196836170501</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>65.02060947003059</v>
@@ -2786,6 +2773,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>89.2317918089857</v>
+      </c>
+      <c r="X12" t="n">
+        <v>612.1491017610846</v>
       </c>
     </row>
     <row r="13">
@@ -2797,9 +2787,6 @@
           <t>Benthos</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
@@ -2849,6 +2836,9 @@
         <v>0</v>
       </c>
       <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2861,11 +2851,8 @@
           <t>Macrozooplankton</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>169.6510695743058</v>
+        <v>23.34359564000601</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>12.54143896805649</v>
@@ -2914,6 +2901,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>17.10408699966879</v>
+      </c>
+      <c r="X14" t="n">
+        <v>169.6510695743057</v>
       </c>
     </row>
     <row r="15">
@@ -2925,11 +2915,8 @@
           <t>Mesozooplankton</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>42.5431325399358</v>
+        <v>10.70524878441424</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6.159994864452676</v>
@@ -2978,6 +2965,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>8.562533087404638</v>
+      </c>
+      <c r="X15" t="n">
+        <v>42.54313253993578</v>
       </c>
     </row>
     <row r="16">
@@ -2989,11 +2979,8 @@
           <t>Microzooplankton</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>7.18811763397654</v>
+        <v>3.505236710255786</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>2.618568894145476</v>
@@ -3043,6 +3030,9 @@
       <c r="V16" s="2" t="n">
         <v>3.752402513345868</v>
       </c>
+      <c r="X16" t="n">
+        <v>7.188117633976538</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -3053,9 +3043,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
@@ -3105,6 +3092,9 @@
         <v>1</v>
       </c>
       <c r="V17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3119,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3257,6 +3247,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -3306,19 +3306,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3391,6 +3394,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9945074102428096</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -3408,10 +3417,10 @@
         <v>106.8935658145757</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67.74393713094588</v>
+        <v>15.77774216008306</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13360.77040045901</v>
+        <v>188.7918671478774</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -3419,7 +3428,6 @@
       <c r="H4" s="2" t="n">
         <v>382.7975624073806</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -3458,6 +3466,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>67.74393713094585</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13360.77040045899</v>
       </c>
     </row>
     <row r="5">
@@ -3476,10 +3490,10 @@
         <v>8069.744768654947</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3353.076745589579</v>
+        <v>202.7227189351667</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14606.18933512097</v>
+        <v>360.8781331868919</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1196.150033880461</v>
@@ -3528,6 +3542,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>3577.262586438605</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3353.076745589576</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14606.18933512095</v>
       </c>
     </row>
     <row r="6">
@@ -3546,10 +3566,10 @@
         <v>23.53177165501262</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17.28795572560303</v>
+        <v>6.455465258311062</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2932.860033251503</v>
+        <v>49.90960645679489</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>52242.45882495401</v>
@@ -3598,6 +3618,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>64410.60914333893</v>
+      </c>
+      <c r="W6" t="n">
+        <v>17.28795572560303</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2932.860033251498</v>
       </c>
     </row>
     <row r="7">
@@ -3616,10 +3642,10 @@
         <v>159.1654933004851</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>97.02603415807211</v>
+        <v>19.9588903763206</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4551.944114809745</v>
+        <v>93.30132467553292</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2184.907112239487</v>
@@ -3668,6 +3694,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>3251.81822584747</v>
+      </c>
+      <c r="W7" t="n">
+        <v>97.02603415807205</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4551.944114809738</v>
       </c>
     </row>
     <row r="8">
@@ -3686,10 +3718,10 @@
         <v>2169.082800394674</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1024.623677556654</v>
+        <v>93.3226625525414</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4487.44340559543</v>
+        <v>180.7275062499169</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>562.1165640253228</v>
@@ -3738,6 +3770,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>788.7056424276601</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1024.623677556653</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4487.443405595425</v>
       </c>
     </row>
     <row r="9">
@@ -3756,10 +3794,10 @@
         <v>434.1284410449114</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>239.9466012833353</v>
+        <v>36.09501383780223</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4086.130831584501</v>
+        <v>138.0060848189007</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>8650.695907550458</v>
@@ -3808,6 +3846,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>10519.60696940031</v>
+      </c>
+      <c r="W9" t="n">
+        <v>239.9466012833352</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4086.130831584496</v>
       </c>
     </row>
     <row r="10">
@@ -3826,10 +3870,10 @@
         <v>708.4825299873116</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>373.3009637075916</v>
+        <v>48.20006810260153</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1450.146971649587</v>
+        <v>85.94316682632287</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>169.4312747480485</v>
@@ -3878,6 +3922,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>204.5504557219762</v>
+      </c>
+      <c r="W10" t="n">
+        <v>373.3009637075913</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1450.146971649585</v>
       </c>
     </row>
     <row r="11">
@@ -3896,10 +3946,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>63.78893224677097</v>
+        <v>15.16874616657383</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>63.78893224677097</v>
+        <v>15.16874616657383</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>292.3976608187135</v>
@@ -3948,6 +3998,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>304.5258437144734</v>
+      </c>
+      <c r="W11" t="n">
+        <v>63.78893224677094</v>
+      </c>
+      <c r="X11" t="n">
+        <v>63.78893224677094</v>
       </c>
     </row>
     <row r="12">
@@ -3966,10 +4022,10 @@
         <v>243.8995815870082</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>142.6113217399421</v>
+        <v>25.67958911775147</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>612.149101761085</v>
+        <v>49.47196836170501</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>65.02060947003059</v>
@@ -4018,6 +4074,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>89.2317918089857</v>
+      </c>
+      <c r="W12" t="n">
+        <v>142.611321739942</v>
+      </c>
+      <c r="X12" t="n">
+        <v>612.1491017610846</v>
       </c>
     </row>
     <row r="13">
@@ -4036,10 +4098,10 @@
         <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7.986797371085044</v>
+        <v>3.894707455839762</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7.986797371085044</v>
+        <v>3.894707455839762</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>55.55555555555555</v>
@@ -4088,6 +4150,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>55.99190381506807</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7.986797371085042</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7.986797371085042</v>
       </c>
     </row>
     <row r="14">
@@ -4106,10 +4174,10 @@
         <v>103.8921932241126</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>66.02513554564123</v>
+        <v>15.51463196456773</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>169.6510695743058</v>
+        <v>23.34359564000601</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>12.54143896805649</v>
@@ -4158,6 +4226,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>17.10408699966879</v>
+      </c>
+      <c r="W14" t="n">
+        <v>66.02513554564121</v>
+      </c>
+      <c r="X14" t="n">
+        <v>169.6510695743057</v>
       </c>
     </row>
     <row r="15">
@@ -4176,10 +4250,10 @@
         <v>50.52631065335679</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34.45146607407247</v>
+        <v>10.13641256356028</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>42.5431325399358</v>
+        <v>10.70524878441424</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6.159994864452676</v>
@@ -4228,6 +4302,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>8.562533087404638</v>
+      </c>
+      <c r="W15" t="n">
+        <v>34.45146607407246</v>
+      </c>
+      <c r="X15" t="n">
+        <v>42.54313253993578</v>
       </c>
     </row>
     <row r="16">
@@ -4246,10 +4326,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.986797371085044</v>
+        <v>3.894707455839762</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.18811763397654</v>
+        <v>3.505236710255786</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>2.618568894145476</v>
@@ -4299,6 +4379,12 @@
       <c r="V16" s="2" t="n">
         <v>3.752402513345868</v>
       </c>
+      <c r="W16" t="n">
+        <v>7.986797371085042</v>
+      </c>
+      <c r="X16" t="n">
+        <v>7.188117633976538</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -4367,6 +4453,12 @@
         <v>1</v>
       </c>
       <c r="V17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4381,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4519,6 +4611,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4568,19 +4670,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4653,6 +4758,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9945074102428096</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -4670,10 +4781,10 @@
         <v>106.8935658145757</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67.74393713094588</v>
+        <v>15.77774216008306</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13365.93093226719</v>
+        <v>191.1940035589384</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -4681,7 +4792,6 @@
       <c r="H4" s="2" t="n">
         <v>384.1421267889958</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -4720,6 +4830,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>67.74393713094585</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13365.93093226717</v>
       </c>
     </row>
     <row r="5">
@@ -4738,10 +4854,10 @@
         <v>8069.744768654947</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3353.076745589579</v>
+        <v>202.7227189351667</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14606.18933512097</v>
+        <v>360.8781331868919</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1196.150033880461</v>
@@ -4790,6 +4906,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>3577.262586438605</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3353.076745589576</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14606.18933512095</v>
       </c>
     </row>
     <row r="6">
@@ -4808,10 +4930,10 @@
         <v>23.53177165501262</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17.28795572560303</v>
+        <v>6.455465258311062</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2940.723259100076</v>
+        <v>53.41574274161492</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>52489.96014453978</v>
@@ -4860,6 +4982,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>64657.19826154041</v>
+      </c>
+      <c r="W6" t="n">
+        <v>17.28795572560303</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2940.723259100072</v>
       </c>
     </row>
     <row r="7">
@@ -4878,10 +5006,10 @@
         <v>159.1654933004851</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>97.02603415807211</v>
+        <v>19.9588903763206</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4553.701210231383</v>
+        <v>94.15816031581767</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>2188.66779600017</v>
@@ -4930,6 +5058,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>3255.60951829227</v>
+      </c>
+      <c r="W7" t="n">
+        <v>97.02603415807205</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4553.701210231377</v>
       </c>
     </row>
     <row r="8">
@@ -4948,10 +5082,10 @@
         <v>2169.082800394674</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1024.623677556654</v>
+        <v>93.3226625525414</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4487.44340559543</v>
+        <v>180.7275062499169</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>562.1165640253228</v>
@@ -5000,6 +5134,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>788.7056424276601</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1024.623677556653</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4487.443405595425</v>
       </c>
     </row>
     <row r="9">
@@ -5018,10 +5158,10 @@
         <v>434.1284410449114</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>239.9466012833353</v>
+        <v>36.09501383780223</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4088.287266874694</v>
+        <v>139.0576558319775</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>8680.685193264744</v>
@@ -5070,6 +5210,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>10549.5688242017</v>
+      </c>
+      <c r="W9" t="n">
+        <v>239.9466012833352</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4088.28726687469</v>
       </c>
     </row>
     <row r="10">
@@ -5088,10 +5234,10 @@
         <v>708.4825299873116</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>373.3009637075916</v>
+        <v>48.20006810260153</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1450.146971649587</v>
+        <v>85.94316682632287</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>169.4312747480485</v>
@@ -5140,6 +5286,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>204.5504557219762</v>
+      </c>
+      <c r="W10" t="n">
+        <v>373.3009637075913</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1450.146971649585</v>
       </c>
     </row>
     <row r="11">
@@ -5158,10 +5310,10 @@
         <v>99.99999999999999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>63.78893224677097</v>
+        <v>15.16874616657383</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>63.78893224677097</v>
+        <v>15.16874616657383</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>292.3976608187135</v>
@@ -5210,6 +5362,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>304.5258437144734</v>
+      </c>
+      <c r="W11" t="n">
+        <v>63.78893224677094</v>
+      </c>
+      <c r="X11" t="n">
+        <v>63.78893224677094</v>
       </c>
     </row>
     <row r="12">
@@ -5228,10 +5386,10 @@
         <v>243.8995815870082</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>142.6113217399421</v>
+        <v>25.67958911775147</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>612.149101761085</v>
+        <v>49.47196836170501</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>65.02060947003059</v>
@@ -5280,6 +5438,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>89.2317918089857</v>
+      </c>
+      <c r="W12" t="n">
+        <v>142.611321739942</v>
+      </c>
+      <c r="X12" t="n">
+        <v>612.1491017610846</v>
       </c>
     </row>
     <row r="13">
@@ -5298,10 +5462,10 @@
         <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7.986797371085044</v>
+        <v>3.894707455839762</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7.986797371085044</v>
+        <v>3.894707455839762</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>55.55555555555555</v>
@@ -5350,6 +5514,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>55.99190381506807</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7.986797371085042</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7.986797371085042</v>
       </c>
     </row>
     <row r="14">
@@ -5368,10 +5538,10 @@
         <v>103.8921932241126</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>66.02513554564123</v>
+        <v>15.51463196456773</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>169.6510695743058</v>
+        <v>23.34359564000601</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>12.54143896805649</v>
@@ -5420,6 +5590,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>17.10408699966879</v>
+      </c>
+      <c r="W14" t="n">
+        <v>66.02513554564121</v>
+      </c>
+      <c r="X14" t="n">
+        <v>169.6510695743057</v>
       </c>
     </row>
     <row r="15">
@@ -5438,10 +5614,10 @@
         <v>50.52631065335679</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34.45146607407247</v>
+        <v>10.13641256356028</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>42.5431325399358</v>
+        <v>10.70524878441424</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>6.159994864452676</v>
@@ -5490,6 +5666,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>8.562533087404638</v>
+      </c>
+      <c r="W15" t="n">
+        <v>34.45146607407246</v>
+      </c>
+      <c r="X15" t="n">
+        <v>42.54313253993578</v>
       </c>
     </row>
     <row r="16">
@@ -5508,10 +5690,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.986797371085044</v>
+        <v>3.894707455839762</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7.18811763397654</v>
+        <v>3.505236710255786</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>2.618568894145476</v>
@@ -5561,6 +5743,12 @@
       <c r="V16" s="2" t="n">
         <v>3.752402513345868</v>
       </c>
+      <c r="W16" t="n">
+        <v>7.986797371085042</v>
+      </c>
+      <c r="X16" t="n">
+        <v>7.188117633976538</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -5629,6 +5817,12 @@
         <v>1</v>
       </c>
       <c r="V17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6101,7 +6295,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.02104337504932972</v>
       </c>
@@ -6227,7 +6420,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Chilean_Patagonia (1980)</t>
@@ -6291,7 +6483,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -6485,7 +6676,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.02128149654405865</v>
       </c>
@@ -6587,7 +6777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6648,14 +6838,12 @@
       <c r="C2" s="2" t="n">
         <v>536.3450509794259</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>20033.51</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.02677239540047779</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -6669,14 +6857,12 @@
       <c r="C3" s="2" t="n">
         <v>1063.209246177555</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>20033.51</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.05307154094202938</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6685,19 +6871,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>447.3436075499878</v>
+        <v>28.9368759133985</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>447.3436075499878</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>28.9368759133985</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>20033.51</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.02232976685313696</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.001444423663821193</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -6706,22 +6890,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2171.978628859558</v>
+        <v>56.62471302876488</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2171.835026242827</v>
+        <v>56.55468618870888</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2159.526616432337</v>
+        <v>55.02650468572452</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>20033.51</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1084101101725472</v>
+        <v>0.002823004365620847</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1077957190942744</v>
+        <v>0.002746723099732624</v>
       </c>
     </row>
     <row r="6">
@@ -7122,6 +7306,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.0392956342489637</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>447.3436075499874</v>
+      </c>
+      <c r="C22" t="n">
+        <v>447.3436075499874</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20033.51</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.02232976685313694</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2171.978628859556</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2171.835026242824</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2159.526616432335</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20033.51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1084101101725471</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1077957190942743</v>
       </c>
     </row>
   </sheetData>
@@ -7257,7 +7485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7293,7 +7521,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -7306,7 +7533,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -7319,7 +7545,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -7332,7 +7557,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -7345,7 +7569,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -7358,7 +7581,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -7371,7 +7593,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -7384,7 +7605,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -7397,7 +7617,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -7441,7 +7660,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7458,7 +7677,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7734,6 +7953,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
